--- a/artfynd/A 42858-2023 artfynd.xlsx
+++ b/artfynd/A 42858-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42858-2023 artfynd.xlsx
+++ b/artfynd/A 42858-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>95466107</v>
       </c>
       <c r="B2" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521179.537817763</v>
+        <v>521179</v>
       </c>
       <c r="R2" t="n">
-        <v>6471799.692656515</v>
+        <v>6471800</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-05-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>93763174</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521140.4822608408</v>
+        <v>521140</v>
       </c>
       <c r="R3" t="n">
-        <v>6471736.566925704</v>
+        <v>6471737</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -868,19 +848,9 @@
           <t>2021-05-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
